--- a/owlcms/src/main/resources/templates/competitionBook/Total-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/competitionBook/Total-LETTER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\competitionBook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB07854-E0F0-41A5-B493-8AC14D3AB703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00FE8298-F0A4-4430-9E11-C0BDECB8D9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="447" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="447" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="C" sheetId="35" r:id="rId1"/>
@@ -372,9 +372,6 @@
     <t>${competition.womenPerTeamElseDefault}</t>
   </si>
   <si>
-    <t>${l.totalRank}</t>
-  </si>
-  <si>
     <t>&lt;jx:forEach items="${mTot}" groupBy="category.code"&gt;</t>
   </si>
   <si>
@@ -526,6 +523,9 @@
   </si>
   <si>
     <t>${l.bestLifterRank &lt; 0 ? t.get("Results.Extra/Invited") : l.bestLifterRank}</t>
+  </si>
+  <si>
+    <t>${l.totalRank &lt; 0 ? 0 : l.totalRank }</t>
   </si>
 </sst>
 </file>
@@ -1617,47 +1617,7 @@
     <cellStyle name="Titre 1 1 1" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
     <cellStyle name="Titre de la feuille" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2211,7 +2171,7 @@
         <v>81</v>
       </c>
       <c r="B3" s="103" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C3" s="103"/>
       <c r="D3" s="103"/>
@@ -2292,7 +2252,7 @@
         <v>89</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M10" s="45" t="s">
         <v>90</v>
@@ -3862,10 +3822,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" t="s">
         <v>114</v>
-      </c>
-      <c r="B1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -5610,7 +5570,7 @@
     </row>
     <row r="3" spans="1:23" s="18" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="57" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B3" s="58"/>
       <c r="C3" s="58"/>
@@ -5638,7 +5598,7 @@
     </row>
     <row r="5" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="61" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B5" s="62"/>
       <c r="C5" s="63"/>
@@ -5665,7 +5625,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -5719,7 +5679,7 @@
         <v>36</v>
       </c>
       <c r="M7" s="55" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N7" s="25" t="s">
         <v>37</v>
@@ -5734,13 +5694,13 @@
         <v>40</v>
       </c>
       <c r="R7" s="55" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="S7" s="23" t="s">
         <v>4</v>
       </c>
       <c r="T7" s="54" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
@@ -6094,21 +6054,13 @@
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B8:C8">
-    <cfRule type="expression" dxfId="12" priority="4" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9:C9">
-    <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="B8:C9">
+    <cfRule type="expression" dxfId="7" priority="1" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:D4">
-    <cfRule type="expression" dxfId="10" priority="2" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="2" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6254,7 +6206,7 @@
     </row>
     <row r="3" spans="1:23" s="18" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="57" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B3" s="58"/>
       <c r="C3" s="58"/>
@@ -6282,7 +6234,7 @@
     </row>
     <row r="5" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="61" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B5" s="62"/>
       <c r="C5" s="63"/>
@@ -6309,7 +6261,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -6361,7 +6313,7 @@
         <v>36</v>
       </c>
       <c r="M7" s="55" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N7" s="25" t="s">
         <v>37</v>
@@ -6376,13 +6328,13 @@
         <v>40</v>
       </c>
       <c r="R7" s="55" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="S7" s="23" t="s">
         <v>4</v>
       </c>
       <c r="T7" s="54" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
@@ -6737,21 +6689,13 @@
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B8:C8">
-    <cfRule type="expression" dxfId="8" priority="4" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9:C9">
-    <cfRule type="expression" dxfId="7" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="B8:C9">
+    <cfRule type="expression" dxfId="5" priority="1" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:D4">
-    <cfRule type="expression" dxfId="6" priority="2" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="2" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6843,7 +6787,7 @@
         <v>65</v>
       </c>
       <c r="R1" s="119" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="S1" s="119"/>
       <c r="U1"/>
@@ -6884,7 +6828,7 @@
       </c>
       <c r="Q2" s="131"/>
       <c r="R2" s="31" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="S2" s="56" t="s">
         <v>67</v>
@@ -6892,7 +6836,7 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -6924,7 +6868,7 @@
       </c>
       <c r="D4" s="17"/>
       <c r="E4" s="27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F4" s="28" t="s">
         <v>2</v>
@@ -6963,10 +6907,10 @@
         <v>4</v>
       </c>
       <c r="R4" s="35" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="S4" s="34" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="V4" s="20" t="s">
         <v>41</v>
@@ -7303,7 +7247,7 @@
     <mergeCell ref="Q1:Q2"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:C4">
-    <cfRule type="expression" dxfId="4" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
       <formula>AND(("$'Hommes Sinclair'.$#REF!$#REF!"),"$'Hommes Sinclair'.$#REF!$#REF!","$'Hommes Sinclair'.$#REF!$#REF!")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7389,7 +7333,7 @@
         <v>65</v>
       </c>
       <c r="R1" s="119" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="S1" s="119"/>
     </row>
@@ -7428,7 +7372,7 @@
       </c>
       <c r="Q2" s="131"/>
       <c r="R2" s="31" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="S2" s="56" t="s">
         <v>67</v>
@@ -7436,7 +7380,7 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -7465,7 +7409,7 @@
       </c>
       <c r="D4" s="17"/>
       <c r="E4" s="27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F4" s="28" t="s">
         <v>2</v>
@@ -7504,10 +7448,10 @@
         <v>4</v>
       </c>
       <c r="R4" s="35" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="S4" s="34" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
@@ -7822,7 +7766,7 @@
     <mergeCell ref="Q1:Q2"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:C4">
-    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
       <formula>AND(("$'Hommes Sinclair'.$#REF!$#REF!"),"$'Hommes Sinclair'.$#REF!$#REF!","$'Hommes Sinclair'.$#REF!$#REF!")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7892,13 +7836,13 @@
         <v>61</v>
       </c>
       <c r="N3" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="O3" s="68" t="s">
         <v>141</v>
       </c>
-      <c r="O3" s="68" t="s">
+      <c r="P3" s="68" t="s">
         <v>142</v>
-      </c>
-      <c r="P3" s="68" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -7931,13 +7875,13 @@
         <v>13</v>
       </c>
       <c r="N5" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="O5" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="O5" s="40" t="s">
+      <c r="P5" s="100" t="s">
         <v>145</v>
-      </c>
-      <c r="P5" s="100" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8007,13 +7951,13 @@
         <v>72</v>
       </c>
       <c r="N10" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="O10" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="O10" s="38" t="s">
+      <c r="P10" s="68" t="s">
         <v>142</v>
-      </c>
-      <c r="P10" s="68" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
@@ -8057,10 +8001,10 @@
         <v>7</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>108</v>
+        <v>159</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L12" s="10" t="s">
         <v>58</v>
@@ -8069,13 +8013,13 @@
         <v>19</v>
       </c>
       <c r="N12" s="66" t="s">
+        <v>146</v>
+      </c>
+      <c r="O12" s="66" t="s">
         <v>147</v>
       </c>
-      <c r="O12" s="66" t="s">
+      <c r="P12" s="66" t="s">
         <v>148</v>
-      </c>
-      <c r="P12" s="66" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8207,13 +8151,13 @@
         <v>61</v>
       </c>
       <c r="N3" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="O3" s="68" t="s">
         <v>141</v>
       </c>
-      <c r="O3" s="68" t="s">
+      <c r="P3" s="68" t="s">
         <v>142</v>
-      </c>
-      <c r="P3" s="68" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -8246,13 +8190,13 @@
         <v>13</v>
       </c>
       <c r="N5" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="O5" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="O5" s="40" t="s">
+      <c r="P5" s="100" t="s">
         <v>145</v>
-      </c>
-      <c r="P5" s="100" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8322,13 +8266,13 @@
         <v>72</v>
       </c>
       <c r="N10" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="O10" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="O10" s="38" t="s">
+      <c r="P10" s="68" t="s">
         <v>142</v>
-      </c>
-      <c r="P10" s="68" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
@@ -8372,10 +8316,10 @@
         <v>7</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>108</v>
+        <v>159</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L12" s="10" t="s">
         <v>58</v>
@@ -8384,13 +8328,13 @@
         <v>19</v>
       </c>
       <c r="N12" s="66" t="s">
+        <v>146</v>
+      </c>
+      <c r="O12" s="66" t="s">
         <v>147</v>
       </c>
-      <c r="O12" s="66" t="s">
+      <c r="P12" s="66" t="s">
         <v>148</v>
-      </c>
-      <c r="P12" s="66" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8525,13 +8469,13 @@
         <v>61</v>
       </c>
       <c r="N3" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="O3" s="68" t="s">
         <v>141</v>
       </c>
-      <c r="O3" s="68" t="s">
+      <c r="P3" s="68" t="s">
         <v>142</v>
-      </c>
-      <c r="P3" s="68" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -8567,13 +8511,13 @@
         <v>13</v>
       </c>
       <c r="N5" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="O5" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="O5" s="40" t="s">
+      <c r="P5" s="100" t="s">
         <v>145</v>
-      </c>
-      <c r="P5" s="100" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8644,13 +8588,13 @@
         <v>72</v>
       </c>
       <c r="N10" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="O10" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="O10" s="38" t="s">
+      <c r="P10" s="68" t="s">
         <v>142</v>
-      </c>
-      <c r="P10" s="68" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
@@ -8694,10 +8638,10 @@
         <v>7</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>108</v>
+        <v>159</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L12" s="10" t="s">
         <v>58</v>
@@ -8706,13 +8650,13 @@
         <v>19</v>
       </c>
       <c r="N12" s="66" t="s">
+        <v>146</v>
+      </c>
+      <c r="O12" s="66" t="s">
         <v>147</v>
       </c>
-      <c r="O12" s="66" t="s">
+      <c r="P12" s="66" t="s">
         <v>148</v>
-      </c>
-      <c r="P12" s="66" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8828,13 +8772,13 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:24" s="69" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="69" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J2" s="70"/>
     </row>
@@ -8864,28 +8808,28 @@
     </row>
     <row r="4" spans="1:24" s="82" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A4" s="73" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B4" s="74"/>
       <c r="C4" s="75"/>
       <c r="D4" s="76" t="s">
+        <v>120</v>
+      </c>
+      <c r="E4" s="77" t="s">
         <v>121</v>
-      </c>
-      <c r="E4" s="77" t="s">
-        <v>122</v>
       </c>
       <c r="F4" s="76" t="s">
         <v>59</v>
       </c>
       <c r="G4" s="78" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H4" s="79"/>
       <c r="I4" s="76" t="s">
+        <v>123</v>
+      </c>
+      <c r="J4" s="73" t="s">
         <v>124</v>
-      </c>
-      <c r="J4" s="73" t="s">
-        <v>125</v>
       </c>
       <c r="K4" s="80"/>
       <c r="L4" s="74"/>
@@ -8900,18 +8844,18 @@
       </c>
       <c r="R4" s="74"/>
       <c r="S4" s="73" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T4" s="80"/>
       <c r="U4" s="73" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="V4" s="81"/>
       <c r="X4" s="75"/>
     </row>
     <row r="5" spans="1:24" s="87" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="83" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B5" s="84"/>
       <c r="C5" s="84"/>
@@ -8927,47 +8871,47 @@
     </row>
     <row r="6" spans="1:24" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="88" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B6" s="89"/>
       <c r="C6" s="90"/>
       <c r="D6" s="91" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" s="92" t="s">
         <v>130</v>
       </c>
-      <c r="E6" s="92" t="s">
+      <c r="F6" s="88" t="s">
         <v>131</v>
       </c>
-      <c r="F6" s="88" t="s">
-        <v>132</v>
-      </c>
       <c r="G6" s="92" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H6" s="90"/>
       <c r="I6" s="94" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J6" s="92" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K6" s="89"/>
       <c r="L6" s="89"/>
       <c r="M6" s="90"/>
       <c r="N6" s="92" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O6" s="89"/>
       <c r="P6" s="90"/>
       <c r="Q6" s="88" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R6" s="89"/>
       <c r="S6" s="93" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="T6" s="89"/>
       <c r="U6" s="95" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="V6" s="90"/>
       <c r="X6" s="90"/>
@@ -8994,7 +8938,7 @@
     </row>
     <row r="8" spans="1:24" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="96" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B8" s="84"/>
       <c r="C8" s="84"/>
@@ -9013,10 +8957,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C5:D5">
-    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/owlcms/src/main/resources/templates/competitionBook/Total-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/competitionBook/Total-LETTER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\competitionBook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00FE8298-F0A4-4430-9E11-C0BDECB8D9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E872DA47-FFCB-4990-98A7-9DCA86C1333A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="447" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="12105" tabRatio="447" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="C" sheetId="35" r:id="rId1"/>
@@ -189,9 +189,6 @@
     <t>${t.get("Lot")}</t>
   </si>
   <si>
-    <t>${t.get("Results.MenPerTeam")}</t>
-  </si>
-  <si>
     <t>${t.get("Results.Teams")}</t>
   </si>
   <si>
@@ -210,9 +207,6 @@
     <t>${t.get("CompetitionBook.MT_RightHeader")} - ${t.get("CompetitionBook.MT_LeftHeader")}</t>
   </si>
   <si>
-    <t>${t.get("Results.WomenPerTeam")}</t>
-  </si>
-  <si>
     <t>${t.get("Gender.F")}</t>
   </si>
   <si>
@@ -366,12 +360,6 @@
     <t>${group.weighInShortDateTime != "" ? (t.get("WeighInTime")+': '+group.weighInShortDateTime) : ""}</t>
   </si>
   <si>
-    <t>${competition.menPerTeamElseDefault}</t>
-  </si>
-  <si>
-    <t>${competition.womenPerTeamElseDefault}</t>
-  </si>
-  <si>
     <t>&lt;jx:forEach items="${mTot}" groupBy="category.code"&gt;</t>
   </si>
   <si>
@@ -526,6 +514,18 @@
   </si>
   <si>
     <t>${l.totalRank &lt; 0 ? 0 : l.totalRank }</t>
+  </si>
+  <si>
+    <t>${t.get("Results.MenBestN")}</t>
+  </si>
+  <si>
+    <t>${competition.menBestNElseDefault}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.WomenBestN")}</t>
+  </si>
+  <si>
+    <t>${competition.womenBestNElseDefault}</t>
   </si>
 </sst>
 </file>
@@ -1498,6 +1498,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1527,29 +1550,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -2126,10 +2126,10 @@
   <sheetData>
     <row r="1" spans="1:19" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B1" s="102" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C1" s="102"/>
       <c r="D1" s="102"/>
@@ -2139,18 +2139,18 @@
       <c r="H1" s="44"/>
       <c r="I1" s="44"/>
       <c r="J1" s="44" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K1" s="45" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="44" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B2" s="103" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C2" s="103"/>
       <c r="D2" s="103"/>
@@ -2160,18 +2160,18 @@
       <c r="H2" s="44"/>
       <c r="I2" s="44"/>
       <c r="J2" s="44" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K2" s="45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="44" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B3" s="103" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C3" s="103"/>
       <c r="D3" s="103"/>
@@ -2198,24 +2198,24 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:19" s="3" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="47" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B8" s="48"/>
       <c r="C8" s="48" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D8" s="45" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G8" s="48"/>
       <c r="H8" s="48"/>
       <c r="I8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J8" s="48"/>
       <c r="L8" s="49"/>
@@ -2240,42 +2240,42 @@
     </row>
     <row r="10" spans="1:19" s="45" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C10" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="45" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="I10" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="L10" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="M10" s="45" t="s">
         <v>88</v>
-      </c>
-      <c r="I10" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="L10" s="44" t="s">
-        <v>116</v>
-      </c>
-      <c r="M10" s="45" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="44" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D11" s="45" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E11" s="1"/>
       <c r="H11" s="44" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I11" s="45" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J11" s="45"/>
       <c r="K11" s="1"/>
       <c r="M11" s="45" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N11" s="1"/>
       <c r="P11"/>
@@ -2285,22 +2285,22 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="44" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D12" s="45" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E12" s="1"/>
       <c r="H12" s="44" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I12" s="45" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J12" s="45"/>
       <c r="K12" s="1"/>
       <c r="M12" s="45" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="45"/>
@@ -2310,15 +2310,15 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="44" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="M13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="N13"/>
       <c r="S13"/>
@@ -2331,7 +2331,7 @@
       <c r="K14" s="45"/>
       <c r="L14" s="45"/>
       <c r="M14" s="45" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N14" s="45"/>
       <c r="O14" s="45"/>
@@ -3822,10 +3822,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -5479,58 +5479,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="111" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="106" t="s">
+      <c r="B1" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="108" t="s">
+      <c r="C1" s="115" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="110" t="s">
+      <c r="D1" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="112" t="s">
+      <c r="E1" s="107" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="107" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="107" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="112" t="s">
+      <c r="H1" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="112" t="s">
+      <c r="I1" s="109" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="112" t="s">
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="109" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="104" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="117" t="s">
-        <v>64</v>
-      </c>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="114" t="s">
-        <v>65</v>
-      </c>
-      <c r="T1" s="115"/>
+      <c r="T1" s="105"/>
     </row>
     <row r="2" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="105"/>
-      <c r="B2" s="107"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
       <c r="I2" s="33">
         <v>1</v>
       </c>
@@ -5541,10 +5541,10 @@
         <v>3</v>
       </c>
       <c r="L2" s="32" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M2" s="56" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N2" s="16">
         <v>1</v>
@@ -5556,21 +5556,21 @@
         <v>3</v>
       </c>
       <c r="Q2" s="32" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="R2" s="56" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="S2" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="T2" s="56" t="s">
         <v>65</v>
-      </c>
-      <c r="T2" s="56" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:23" s="18" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="57" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B3" s="58"/>
       <c r="C3" s="58"/>
@@ -5598,7 +5598,7 @@
     </row>
     <row r="5" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="61" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B5" s="62"/>
       <c r="C5" s="63"/>
@@ -5625,7 +5625,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -5679,7 +5679,7 @@
         <v>36</v>
       </c>
       <c r="M7" s="55" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="N7" s="25" t="s">
         <v>37</v>
@@ -5694,13 +5694,13 @@
         <v>40</v>
       </c>
       <c r="R7" s="55" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="S7" s="23" t="s">
         <v>4</v>
       </c>
       <c r="T7" s="54" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
@@ -5759,11 +5759,11 @@
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1"/>
-      <c r="R15" s="116"/>
+      <c r="R15" s="106"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C16" s="1"/>
-      <c r="R16" s="116"/>
+      <c r="R16" s="106"/>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C17" s="1"/>
@@ -6041,6 +6041,11 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="R15:R16"/>
     <mergeCell ref="F1:F2"/>
@@ -6048,11 +6053,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:M1"/>
     <mergeCell ref="N1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="B8:C9">
     <cfRule type="expression" dxfId="7" priority="1" stopIfTrue="1">
@@ -6115,58 +6115,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="111" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="106" t="s">
+      <c r="B1" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="108" t="s">
+      <c r="C1" s="115" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="110" t="s">
+      <c r="D1" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="112" t="s">
+      <c r="E1" s="107" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="107" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="107" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="112" t="s">
+      <c r="H1" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="112" t="s">
+      <c r="I1" s="109" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="112" t="s">
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="109" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="104" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="117" t="s">
-        <v>64</v>
-      </c>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="114" t="s">
-        <v>65</v>
-      </c>
-      <c r="T1" s="115"/>
+      <c r="T1" s="105"/>
     </row>
     <row r="2" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="105"/>
-      <c r="B2" s="107"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
       <c r="I2" s="33">
         <v>1</v>
       </c>
@@ -6177,10 +6177,10 @@
         <v>3</v>
       </c>
       <c r="L2" s="32" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M2" s="56" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N2" s="16">
         <v>1</v>
@@ -6192,21 +6192,21 @@
         <v>3</v>
       </c>
       <c r="Q2" s="32" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="R2" s="56" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="S2" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="T2" s="56" t="s">
         <v>65</v>
-      </c>
-      <c r="T2" s="56" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:23" s="18" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="57" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B3" s="58"/>
       <c r="C3" s="58"/>
@@ -6234,7 +6234,7 @@
     </row>
     <row r="5" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="61" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B5" s="62"/>
       <c r="C5" s="63"/>
@@ -6261,7 +6261,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -6313,7 +6313,7 @@
         <v>36</v>
       </c>
       <c r="M7" s="55" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="N7" s="25" t="s">
         <v>37</v>
@@ -6328,13 +6328,13 @@
         <v>40</v>
       </c>
       <c r="R7" s="55" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="S7" s="23" t="s">
         <v>4</v>
       </c>
       <c r="T7" s="54" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
@@ -6394,11 +6394,11 @@
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C16" s="1"/>
-      <c r="P16" s="116"/>
+      <c r="P16" s="106"/>
     </row>
     <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1"/>
-      <c r="P17" s="116"/>
+      <c r="P17" s="106"/>
     </row>
     <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1"/>
@@ -6676,6 +6676,11 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="12">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="P16:P17"/>
     <mergeCell ref="F1:F2"/>
@@ -6683,11 +6688,6 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:M1"/>
     <mergeCell ref="N1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="B8:C9">
     <cfRule type="expression" dxfId="5" priority="1" stopIfTrue="1">
@@ -6756,38 +6756,38 @@
       <c r="C1" s="122" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="110" t="s">
+      <c r="D1" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="112" t="s">
+      <c r="E1" s="107" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="125" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="126" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="125" t="s">
+      <c r="H1" s="127" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="126" t="s">
+      <c r="I1" s="129" t="s">
         <v>61</v>
-      </c>
-      <c r="H1" s="127" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="129" t="s">
-        <v>63</v>
       </c>
       <c r="J1" s="129"/>
       <c r="K1" s="129"/>
       <c r="L1" s="129"/>
       <c r="M1" s="129" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N1" s="129"/>
       <c r="O1" s="129"/>
       <c r="P1" s="129"/>
       <c r="Q1" s="130" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="R1" s="119" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="S1" s="119"/>
       <c r="U1"/>
@@ -6798,7 +6798,7 @@
       <c r="B2" s="121"/>
       <c r="C2" s="123"/>
       <c r="D2" s="124"/>
-      <c r="E2" s="112"/>
+      <c r="E2" s="107"/>
       <c r="F2" s="125"/>
       <c r="G2" s="126"/>
       <c r="H2" s="128"/>
@@ -6828,15 +6828,15 @@
       </c>
       <c r="Q2" s="131"/>
       <c r="R2" s="31" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="S2" s="56" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="D4" s="17"/>
       <c r="E4" s="27" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F4" s="28" t="s">
         <v>2</v>
@@ -6907,10 +6907,10 @@
         <v>4</v>
       </c>
       <c r="R4" s="35" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="S4" s="34" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="V4" s="20" t="s">
         <v>41</v>
@@ -7302,38 +7302,38 @@
       <c r="C1" s="122" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="110" t="s">
+      <c r="D1" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="112" t="s">
+      <c r="E1" s="107" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="125" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="126" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="125" t="s">
+      <c r="H1" s="127" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="126" t="s">
+      <c r="I1" s="129" t="s">
         <v>61</v>
-      </c>
-      <c r="H1" s="127" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="129" t="s">
-        <v>63</v>
       </c>
       <c r="J1" s="129"/>
       <c r="K1" s="129"/>
       <c r="L1" s="129"/>
       <c r="M1" s="129" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N1" s="129"/>
       <c r="O1" s="129"/>
       <c r="P1" s="129"/>
       <c r="Q1" s="130" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="R1" s="119" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="S1" s="119"/>
     </row>
@@ -7342,7 +7342,7 @@
       <c r="B2" s="121"/>
       <c r="C2" s="123"/>
       <c r="D2" s="124"/>
-      <c r="E2" s="112"/>
+      <c r="E2" s="107"/>
       <c r="F2" s="125"/>
       <c r="G2" s="126"/>
       <c r="H2" s="128"/>
@@ -7372,15 +7372,15 @@
       </c>
       <c r="Q2" s="131"/>
       <c r="R2" s="31" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="S2" s="56" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D4" s="17"/>
       <c r="E4" s="27" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F4" s="28" t="s">
         <v>2</v>
@@ -7448,10 +7448,10 @@
         <v>4</v>
       </c>
       <c r="R4" s="35" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="S4" s="34" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
@@ -7810,7 +7810,7 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -7821,28 +7821,28 @@
     </row>
     <row r="3" spans="1:19" s="6" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D3" s="68" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M3" s="43" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N3" s="42" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="O3" s="68" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P3" s="68" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -7875,13 +7875,13 @@
         <v>13</v>
       </c>
       <c r="N5" s="40" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="O5" s="40" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="P5" s="100" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -7904,7 +7904,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -7912,7 +7912,7 @@
     <row r="9" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:19" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="67" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B10" s="39" t="s">
         <v>45</v>
@@ -7921,16 +7921,16 @@
         <v>44</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>8</v>
@@ -7939,25 +7939,25 @@
         <v>15</v>
       </c>
       <c r="J10" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="L10" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="M10" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="L10" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="M10" s="38" t="s">
-        <v>72</v>
-      </c>
       <c r="N10" s="38" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="O10" s="38" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P10" s="68" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
@@ -8001,25 +8001,25 @@
         <v>7</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M12" s="66" t="s">
         <v>19</v>
       </c>
       <c r="N12" s="66" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="O12" s="66" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="P12" s="66" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8057,7 +8057,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
@@ -8065,7 +8065,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" t="s">
@@ -8074,10 +8074,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>156</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -8125,7 +8125,7 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -8136,28 +8136,28 @@
     </row>
     <row r="3" spans="1:19" s="6" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D3" s="68" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M3" s="43" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N3" s="42" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="O3" s="68" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P3" s="68" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -8190,13 +8190,13 @@
         <v>13</v>
       </c>
       <c r="N5" s="40" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="O5" s="40" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="P5" s="100" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8219,7 +8219,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -8227,7 +8227,7 @@
     <row r="9" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:19" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="67" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B10" s="39" t="s">
         <v>45</v>
@@ -8236,16 +8236,16 @@
         <v>44</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>8</v>
@@ -8254,25 +8254,25 @@
         <v>15</v>
       </c>
       <c r="J10" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="L10" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="M10" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="L10" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="M10" s="38" t="s">
-        <v>72</v>
-      </c>
       <c r="N10" s="38" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="O10" s="38" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P10" s="68" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
@@ -8316,25 +8316,25 @@
         <v>7</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M12" s="66" t="s">
         <v>19</v>
       </c>
       <c r="N12" s="66" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="O12" s="66" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="P12" s="66" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8372,7 +8372,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
         <v>25</v>
@@ -8380,7 +8380,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" t="s">
@@ -8389,10 +8389,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>158</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -8440,7 +8440,7 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -8451,31 +8451,31 @@
     </row>
     <row r="3" spans="1:19" s="6" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E3" s="68" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M3" s="43" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N3" s="42" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="O3" s="68" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P3" s="68" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -8511,13 +8511,13 @@
         <v>13</v>
       </c>
       <c r="N5" s="40" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="O5" s="40" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="P5" s="100" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8541,7 +8541,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -8549,7 +8549,7 @@
     <row r="9" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:19" ht="41.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="67" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B10" s="39" t="s">
         <v>45</v>
@@ -8558,16 +8558,16 @@
         <v>44</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>8</v>
@@ -8576,25 +8576,25 @@
         <v>15</v>
       </c>
       <c r="J10" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="L10" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="M10" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="L10" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="M10" s="38" t="s">
-        <v>72</v>
-      </c>
       <c r="N10" s="38" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="O10" s="38" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P10" s="68" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
@@ -8638,25 +8638,25 @@
         <v>7</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M12" s="66" t="s">
         <v>19</v>
       </c>
       <c r="N12" s="66" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="O12" s="66" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="P12" s="66" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8694,7 +8694,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
         <v>43</v>
@@ -8702,7 +8702,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" t="s">
@@ -8711,18 +8711,18 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>156</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>158</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -8772,13 +8772,13 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:24" s="69" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="69" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J2" s="70"/>
     </row>
@@ -8808,54 +8808,54 @@
     </row>
     <row r="4" spans="1:24" s="82" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A4" s="73" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B4" s="74"/>
       <c r="C4" s="75"/>
       <c r="D4" s="76" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E4" s="77" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F4" s="76" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G4" s="78" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H4" s="79"/>
       <c r="I4" s="76" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J4" s="73" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="K4" s="80"/>
       <c r="L4" s="74"/>
       <c r="M4" s="75"/>
       <c r="N4" s="73" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O4" s="74"/>
       <c r="P4" s="81"/>
       <c r="Q4" s="73" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="R4" s="74"/>
       <c r="S4" s="73" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="T4" s="80"/>
       <c r="U4" s="73" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="V4" s="81"/>
       <c r="X4" s="75"/>
     </row>
     <row r="5" spans="1:24" s="87" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="83" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B5" s="84"/>
       <c r="C5" s="84"/>
@@ -8871,47 +8871,47 @@
     </row>
     <row r="6" spans="1:24" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="88" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B6" s="89"/>
       <c r="C6" s="90"/>
       <c r="D6" s="91" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E6" s="92" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F6" s="88" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G6" s="92" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H6" s="90"/>
       <c r="I6" s="94" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="J6" s="92" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="K6" s="89"/>
       <c r="L6" s="89"/>
       <c r="M6" s="90"/>
       <c r="N6" s="92" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="O6" s="89"/>
       <c r="P6" s="90"/>
       <c r="Q6" s="88" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="R6" s="89"/>
       <c r="S6" s="93" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="T6" s="89"/>
       <c r="U6" s="95" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="V6" s="90"/>
       <c r="X6" s="90"/>
@@ -8938,7 +8938,7 @@
     </row>
     <row r="8" spans="1:24" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="96" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B8" s="84"/>
       <c r="C8" s="84"/>
